--- a/WEB-INF/templateFile/KinYukyuKyukaDaicho.xlsx
+++ b/WEB-INF/templateFile/KinYukyuKyukaDaicho.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.200.3\0-546-0\勤怠管理システム\01_成果物\00_帳票テンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\Kintai\workspace\Kintai\WEB-INF\templateFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BEB0C7-9630-4B34-8627-78EFDF61BA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17025" windowHeight="11535"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,6 +22,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -112,7 +116,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -243,7 +247,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -298,6 +302,18 @@
     <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -307,9 +323,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -319,18 +332,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -348,6 +349,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -628,73 +635,73 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AX65"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="50" width="2.625" style="1" customWidth="1"/>
+    <col min="1" max="50" width="2.59765625" style="1" customWidth="1"/>
     <col min="51" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:50" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="24"/>
-      <c r="AB1" s="24"/>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="24"/>
-      <c r="AF1" s="24"/>
-      <c r="AG1" s="24"/>
-      <c r="AH1" s="24"/>
-      <c r="AI1" s="24"/>
-      <c r="AJ1" s="24"/>
-      <c r="AK1" s="24"/>
-      <c r="AL1" s="24"/>
-      <c r="AM1" s="24"/>
-      <c r="AN1" s="24"/>
-      <c r="AO1" s="24"/>
-      <c r="AP1" s="24"/>
-      <c r="AQ1" s="24"/>
-      <c r="AR1" s="24"/>
-      <c r="AS1" s="24"/>
-      <c r="AT1" s="24"/>
-      <c r="AU1" s="24"/>
-      <c r="AV1" s="24"/>
-      <c r="AW1" s="24"/>
-      <c r="AX1" s="24"/>
-    </row>
-    <row r="2" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="27"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
+      <c r="AH1" s="27"/>
+      <c r="AI1" s="27"/>
+      <c r="AJ1" s="27"/>
+      <c r="AK1" s="27"/>
+      <c r="AL1" s="27"/>
+      <c r="AM1" s="27"/>
+      <c r="AN1" s="27"/>
+      <c r="AO1" s="27"/>
+      <c r="AP1" s="27"/>
+      <c r="AQ1" s="27"/>
+      <c r="AR1" s="27"/>
+      <c r="AS1" s="27"/>
+      <c r="AT1" s="27"/>
+      <c r="AU1" s="27"/>
+      <c r="AV1" s="27"/>
+      <c r="AW1" s="27"/>
+      <c r="AX1" s="27"/>
+    </row>
+    <row r="2" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -715,110 +722,110 @@
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
-      <c r="AM3" s="19"/>
-      <c r="AN3" s="19"/>
-      <c r="AO3" s="19"/>
-      <c r="AP3" s="19"/>
-      <c r="AQ3" s="19"/>
-      <c r="AR3" s="19"/>
-      <c r="AS3" s="20"/>
-      <c r="AT3" s="20"/>
-      <c r="AU3" s="20"/>
-      <c r="AV3" s="20"/>
-      <c r="AW3" s="20"/>
-      <c r="AX3" s="20"/>
-    </row>
-    <row r="4" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="AM4" s="23"/>
-      <c r="AN4" s="23"/>
-      <c r="AO4" s="23"/>
-      <c r="AP4" s="23"/>
-      <c r="AQ4" s="23"/>
-      <c r="AR4" s="23"/>
-      <c r="AS4" s="23"/>
-      <c r="AT4" s="23"/>
-      <c r="AU4" s="23"/>
-      <c r="AV4" s="23"/>
-      <c r="AW4" s="23"/>
-      <c r="AX4" s="23"/>
-    </row>
-    <row r="5" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="AE5" s="32" t="s">
+      <c r="AM3" s="23"/>
+      <c r="AN3" s="23"/>
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="24"/>
+      <c r="AT3" s="24"/>
+      <c r="AU3" s="24"/>
+      <c r="AV3" s="24"/>
+      <c r="AW3" s="24"/>
+      <c r="AX3" s="24"/>
+    </row>
+    <row r="4" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="AM4" s="26"/>
+      <c r="AN4" s="26"/>
+      <c r="AO4" s="26"/>
+      <c r="AP4" s="26"/>
+      <c r="AQ4" s="26"/>
+      <c r="AR4" s="26"/>
+      <c r="AS4" s="26"/>
+      <c r="AT4" s="26"/>
+      <c r="AU4" s="26"/>
+      <c r="AV4" s="26"/>
+      <c r="AW4" s="26"/>
+      <c r="AX4" s="26"/>
+    </row>
+    <row r="5" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="34"/>
+      <c r="AE5" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="AF5" s="33"/>
-      <c r="AG5" s="33"/>
-      <c r="AH5" s="34"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="30"/>
-      <c r="AK5" s="30"/>
-      <c r="AL5" s="31"/>
-      <c r="AM5" s="22"/>
-      <c r="AN5" s="22"/>
-      <c r="AO5" s="22"/>
-      <c r="AP5" s="22"/>
-      <c r="AQ5" s="22"/>
-      <c r="AR5" s="22"/>
-      <c r="AS5" s="22"/>
-      <c r="AT5" s="22"/>
-      <c r="AU5" s="22"/>
-      <c r="AV5" s="22"/>
-      <c r="AW5" s="22"/>
-      <c r="AX5" s="22"/>
-    </row>
-    <row r="6" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="7" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="25" t="s">
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="33"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="30"/>
+      <c r="AM5" s="34"/>
+      <c r="AN5" s="34"/>
+      <c r="AO5" s="34"/>
+      <c r="AP5" s="34"/>
+      <c r="AQ5" s="34"/>
+      <c r="AR5" s="34"/>
+      <c r="AS5" s="34"/>
+      <c r="AT5" s="34"/>
+      <c r="AU5" s="34"/>
+      <c r="AV5" s="34"/>
+      <c r="AW5" s="34"/>
+      <c r="AX5" s="34"/>
+    </row>
+    <row r="6" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
       <c r="U7" s="10"/>
@@ -833,20 +840,20 @@
       <c r="AD7" s="10"/>
       <c r="AE7" s="10"/>
     </row>
-    <row r="8" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:50" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="18" t="s">
+    <row r="8" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="9" spans="1:50" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
@@ -857,18 +864,18 @@
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
-      <c r="U9" s="18" t="s">
+      <c r="U9" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="V9" s="18"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="18"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="18"/>
-      <c r="AA9" s="18"/>
-      <c r="AB9" s="18"/>
-      <c r="AC9" s="18"/>
-      <c r="AD9" s="18"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
       <c r="AG9" s="7"/>
@@ -879,36 +886,36 @@
       <c r="AL9" s="7"/>
       <c r="AM9" s="7"/>
       <c r="AN9" s="7"/>
-      <c r="AO9" s="18" t="s">
+      <c r="AO9" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="AP9" s="18"/>
-      <c r="AQ9" s="18"/>
-      <c r="AR9" s="18"/>
-      <c r="AS9" s="18"/>
-      <c r="AT9" s="18"/>
-      <c r="AU9" s="18"/>
-      <c r="AV9" s="18"/>
-      <c r="AW9" s="18"/>
-      <c r="AX9" s="18"/>
-    </row>
-    <row r="10" spans="1:50" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="18" t="s">
+      <c r="AP9" s="22"/>
+      <c r="AQ9" s="22"/>
+      <c r="AR9" s="22"/>
+      <c r="AS9" s="22"/>
+      <c r="AT9" s="22"/>
+      <c r="AU9" s="22"/>
+      <c r="AV9" s="22"/>
+      <c r="AW9" s="22"/>
+      <c r="AX9" s="22"/>
+    </row>
+    <row r="10" spans="1:50" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18" t="s">
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
@@ -919,22 +926,22 @@
       <c r="R10" s="10"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
-      <c r="U10" s="18" t="s">
+      <c r="U10" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="V10" s="18"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="18" t="s">
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="Y10" s="18"/>
-      <c r="Z10" s="18"/>
-      <c r="AA10" s="18" t="s">
+      <c r="Y10" s="22"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="AB10" s="18"/>
-      <c r="AC10" s="18"/>
-      <c r="AD10" s="18"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
       <c r="AG10" s="7"/>
@@ -945,24 +952,24 @@
       <c r="AL10" s="7"/>
       <c r="AM10" s="7"/>
       <c r="AN10" s="7"/>
-      <c r="AO10" s="18" t="s">
+      <c r="AO10" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="AP10" s="18"/>
-      <c r="AQ10" s="18"/>
-      <c r="AR10" s="18" t="s">
+      <c r="AP10" s="22"/>
+      <c r="AQ10" s="22"/>
+      <c r="AR10" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="AS10" s="18"/>
-      <c r="AT10" s="18"/>
-      <c r="AU10" s="18" t="s">
+      <c r="AS10" s="22"/>
+      <c r="AT10" s="22"/>
+      <c r="AU10" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="AV10" s="18"/>
-      <c r="AW10" s="18"/>
-      <c r="AX10" s="18"/>
-    </row>
-    <row r="11" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AV10" s="22"/>
+      <c r="AW10" s="22"/>
+      <c r="AX10" s="22"/>
+    </row>
+    <row r="11" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -1014,7 +1021,7 @@
       <c r="AW11" s="17"/>
       <c r="AX11" s="17"/>
     </row>
-    <row r="12" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -1066,7 +1073,7 @@
       <c r="AW12" s="17"/>
       <c r="AX12" s="17"/>
     </row>
-    <row r="13" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -1118,7 +1125,7 @@
       <c r="AW13" s="17"/>
       <c r="AX13" s="17"/>
     </row>
-    <row r="14" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -1170,7 +1177,7 @@
       <c r="AW14" s="17"/>
       <c r="AX14" s="17"/>
     </row>
-    <row r="15" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="15"/>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
@@ -1222,7 +1229,7 @@
       <c r="AW15" s="17"/>
       <c r="AX15" s="17"/>
     </row>
-    <row r="16" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="15"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
@@ -1274,7 +1281,7 @@
       <c r="AW16" s="17"/>
       <c r="AX16" s="17"/>
     </row>
-    <row r="17" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="15"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -1326,7 +1333,7 @@
       <c r="AW17" s="17"/>
       <c r="AX17" s="17"/>
     </row>
-    <row r="18" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -1378,7 +1385,7 @@
       <c r="AW18" s="17"/>
       <c r="AX18" s="17"/>
     </row>
-    <row r="19" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -1430,7 +1437,7 @@
       <c r="AW19" s="17"/>
       <c r="AX19" s="17"/>
     </row>
-    <row r="20" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="15"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -1482,7 +1489,7 @@
       <c r="AW20" s="17"/>
       <c r="AX20" s="17"/>
     </row>
-    <row r="21" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -1534,7 +1541,7 @@
       <c r="AW21" s="17"/>
       <c r="AX21" s="17"/>
     </row>
-    <row r="22" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="15"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -1586,7 +1593,7 @@
       <c r="AW22" s="17"/>
       <c r="AX22" s="17"/>
     </row>
-    <row r="23" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -1638,7 +1645,7 @@
       <c r="AW23" s="17"/>
       <c r="AX23" s="17"/>
     </row>
-    <row r="24" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -1690,7 +1697,7 @@
       <c r="AW24" s="17"/>
       <c r="AX24" s="17"/>
     </row>
-    <row r="25" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -1742,7 +1749,7 @@
       <c r="AW25" s="17"/>
       <c r="AX25" s="17"/>
     </row>
-    <row r="26" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -1794,7 +1801,7 @@
       <c r="AW26" s="17"/>
       <c r="AX26" s="17"/>
     </row>
-    <row r="27" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="15"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -1846,7 +1853,7 @@
       <c r="AW27" s="17"/>
       <c r="AX27" s="17"/>
     </row>
-    <row r="28" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -1898,7 +1905,7 @@
       <c r="AW28" s="17"/>
       <c r="AX28" s="17"/>
     </row>
-    <row r="29" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -1950,7 +1957,7 @@
       <c r="AW29" s="17"/>
       <c r="AX29" s="17"/>
     </row>
-    <row r="30" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="15"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -2002,7 +2009,7 @@
       <c r="AW30" s="17"/>
       <c r="AX30" s="17"/>
     </row>
-    <row r="31" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="7"/>
@@ -2054,27 +2061,27 @@
       <c r="AW31" s="7"/>
       <c r="AX31" s="7"/>
     </row>
-    <row r="32" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="25" t="s">
+    <row r="32" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="21"/>
       <c r="S32" s="9"/>
       <c r="T32" s="14"/>
       <c r="U32" s="14"/>
@@ -2108,7 +2115,7 @@
       <c r="AW32" s="7"/>
       <c r="AX32" s="7"/>
     </row>
-    <row r="33" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="7"/>
@@ -2160,7 +2167,7 @@
       <c r="AW33" s="7"/>
       <c r="AX33" s="7"/>
     </row>
-    <row r="34" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="7"/>
@@ -2212,7 +2219,7 @@
       <c r="AW34" s="7"/>
       <c r="AX34" s="7"/>
     </row>
-    <row r="35" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="7"/>
@@ -2264,7 +2271,7 @@
       <c r="AW35" s="7"/>
       <c r="AX35" s="7"/>
     </row>
-    <row r="36" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="13"/>
       <c r="B36" s="13"/>
       <c r="C36" s="7"/>
@@ -2316,7 +2323,7 @@
       <c r="AW36" s="7"/>
       <c r="AX36" s="7"/>
     </row>
-    <row r="37" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="13"/>
       <c r="B37" s="13"/>
       <c r="C37" s="7"/>
@@ -2368,7 +2375,7 @@
       <c r="AW37" s="7"/>
       <c r="AX37" s="7"/>
     </row>
-    <row r="38" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="13"/>
       <c r="B38" s="13"/>
       <c r="C38" s="7"/>
@@ -2420,7 +2427,7 @@
       <c r="AW38" s="7"/>
       <c r="AX38" s="7"/>
     </row>
-    <row r="39" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="13"/>
       <c r="B39" s="13"/>
       <c r="C39" s="7"/>
@@ -2472,7 +2479,7 @@
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
     </row>
-    <row r="40" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="13"/>
       <c r="B40" s="13"/>
       <c r="C40" s="7"/>
@@ -2524,7 +2531,7 @@
       <c r="AW40" s="7"/>
       <c r="AX40" s="7"/>
     </row>
-    <row r="41" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="13"/>
       <c r="B41" s="13"/>
       <c r="C41" s="7"/>
@@ -2576,7 +2583,7 @@
       <c r="AW41" s="7"/>
       <c r="AX41" s="7"/>
     </row>
-    <row r="42" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -2618,180 +2625,64 @@
       <c r="AM42" s="4"/>
       <c r="AN42" s="4"/>
     </row>
-    <row r="43" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="46" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="47" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="43" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="44" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="45" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="46" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="47" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="48" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="206">
-    <mergeCell ref="U17:W17"/>
-    <mergeCell ref="X17:Z17"/>
-    <mergeCell ref="AA17:AD17"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="U21:W21"/>
-    <mergeCell ref="X21:Z21"/>
-    <mergeCell ref="AA21:AD21"/>
-    <mergeCell ref="U22:W22"/>
-    <mergeCell ref="X22:Z22"/>
-    <mergeCell ref="AA22:AD22"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="X14:Z14"/>
-    <mergeCell ref="AA14:AD14"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="X15:Z15"/>
-    <mergeCell ref="AA15:AD15"/>
-    <mergeCell ref="U16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AA16:AD16"/>
-    <mergeCell ref="X26:Z26"/>
-    <mergeCell ref="AA26:AD26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="X30:Z30"/>
-    <mergeCell ref="AA30:AD30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="J32:R32"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="U26:W26"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="U9:AD9"/>
-    <mergeCell ref="U10:W10"/>
-    <mergeCell ref="X10:Z10"/>
-    <mergeCell ref="AA10:AD10"/>
-    <mergeCell ref="AO9:AX9"/>
-    <mergeCell ref="AO10:AQ10"/>
-    <mergeCell ref="AM3:AR3"/>
-    <mergeCell ref="AS3:AX3"/>
-    <mergeCell ref="K5:U5"/>
-    <mergeCell ref="AM4:AX4"/>
-    <mergeCell ref="AM5:AX5"/>
-    <mergeCell ref="A1:AX1"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="J7:R7"/>
-    <mergeCell ref="AI5:AL5"/>
-    <mergeCell ref="AE5:AH5"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="AR10:AT10"/>
-    <mergeCell ref="AU10:AX10"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="AA11:AD11"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="X12:Z12"/>
-    <mergeCell ref="AA12:AD12"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="X13:Z13"/>
-    <mergeCell ref="AA13:AD13"/>
-    <mergeCell ref="AO11:AQ11"/>
-    <mergeCell ref="AR11:AT11"/>
-    <mergeCell ref="AU11:AX11"/>
-    <mergeCell ref="AO12:AQ12"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="U18:W18"/>
-    <mergeCell ref="X18:Z18"/>
-    <mergeCell ref="AA18:AD18"/>
-    <mergeCell ref="U19:W19"/>
-    <mergeCell ref="X19:Z19"/>
-    <mergeCell ref="AA19:AD19"/>
-    <mergeCell ref="U20:W20"/>
-    <mergeCell ref="X20:Z20"/>
-    <mergeCell ref="AA20:AD20"/>
-    <mergeCell ref="U23:W23"/>
-    <mergeCell ref="X23:Z23"/>
-    <mergeCell ref="AA23:AD23"/>
-    <mergeCell ref="U24:W24"/>
-    <mergeCell ref="X24:Z24"/>
-    <mergeCell ref="AA24:AD24"/>
-    <mergeCell ref="U25:W25"/>
-    <mergeCell ref="X25:Z25"/>
-    <mergeCell ref="AA25:AD25"/>
-    <mergeCell ref="U27:W27"/>
-    <mergeCell ref="X27:Z27"/>
-    <mergeCell ref="AA27:AD27"/>
-    <mergeCell ref="U28:W28"/>
-    <mergeCell ref="X28:Z28"/>
-    <mergeCell ref="AA28:AD28"/>
-    <mergeCell ref="U29:W29"/>
-    <mergeCell ref="X29:Z29"/>
+    <mergeCell ref="AO29:AQ29"/>
+    <mergeCell ref="AR29:AT29"/>
+    <mergeCell ref="AU29:AX29"/>
+    <mergeCell ref="AO30:AQ30"/>
+    <mergeCell ref="AR30:AT30"/>
+    <mergeCell ref="AU30:AX30"/>
+    <mergeCell ref="AO26:AQ26"/>
+    <mergeCell ref="AR26:AT26"/>
+    <mergeCell ref="AU26:AX26"/>
+    <mergeCell ref="AO27:AQ27"/>
+    <mergeCell ref="AR27:AT27"/>
+    <mergeCell ref="AU27:AX27"/>
+    <mergeCell ref="AO28:AQ28"/>
+    <mergeCell ref="AR28:AT28"/>
+    <mergeCell ref="AU28:AX28"/>
+    <mergeCell ref="AO23:AQ23"/>
+    <mergeCell ref="AR23:AT23"/>
+    <mergeCell ref="AU23:AX23"/>
+    <mergeCell ref="AO24:AQ24"/>
+    <mergeCell ref="AR24:AT24"/>
+    <mergeCell ref="AU24:AX24"/>
+    <mergeCell ref="AO25:AQ25"/>
+    <mergeCell ref="AR25:AT25"/>
+    <mergeCell ref="AU25:AX25"/>
+    <mergeCell ref="AO20:AQ20"/>
+    <mergeCell ref="AR20:AT20"/>
+    <mergeCell ref="AU20:AX20"/>
+    <mergeCell ref="AO21:AQ21"/>
+    <mergeCell ref="AR21:AT21"/>
+    <mergeCell ref="AU21:AX21"/>
+    <mergeCell ref="AO22:AQ22"/>
+    <mergeCell ref="AR22:AT22"/>
+    <mergeCell ref="AU22:AX22"/>
     <mergeCell ref="AA29:AD29"/>
     <mergeCell ref="AR12:AT12"/>
     <mergeCell ref="AU12:AX12"/>
@@ -2816,42 +2707,158 @@
     <mergeCell ref="AO19:AQ19"/>
     <mergeCell ref="AR19:AT19"/>
     <mergeCell ref="AU19:AX19"/>
-    <mergeCell ref="AO20:AQ20"/>
-    <mergeCell ref="AR20:AT20"/>
-    <mergeCell ref="AU20:AX20"/>
-    <mergeCell ref="AO21:AQ21"/>
-    <mergeCell ref="AR21:AT21"/>
-    <mergeCell ref="AU21:AX21"/>
-    <mergeCell ref="AO22:AQ22"/>
-    <mergeCell ref="AR22:AT22"/>
-    <mergeCell ref="AU22:AX22"/>
-    <mergeCell ref="AO23:AQ23"/>
-    <mergeCell ref="AR23:AT23"/>
-    <mergeCell ref="AU23:AX23"/>
-    <mergeCell ref="AO24:AQ24"/>
-    <mergeCell ref="AR24:AT24"/>
-    <mergeCell ref="AU24:AX24"/>
-    <mergeCell ref="AO25:AQ25"/>
-    <mergeCell ref="AR25:AT25"/>
-    <mergeCell ref="AU25:AX25"/>
-    <mergeCell ref="AO26:AQ26"/>
-    <mergeCell ref="AR26:AT26"/>
-    <mergeCell ref="AU26:AX26"/>
-    <mergeCell ref="AO27:AQ27"/>
-    <mergeCell ref="AR27:AT27"/>
-    <mergeCell ref="AU27:AX27"/>
-    <mergeCell ref="AO28:AQ28"/>
-    <mergeCell ref="AR28:AT28"/>
-    <mergeCell ref="AU28:AX28"/>
-    <mergeCell ref="AO29:AQ29"/>
-    <mergeCell ref="AR29:AT29"/>
-    <mergeCell ref="AU29:AX29"/>
-    <mergeCell ref="AO30:AQ30"/>
-    <mergeCell ref="AR30:AT30"/>
-    <mergeCell ref="AU30:AX30"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="AA23:AD23"/>
+    <mergeCell ref="U24:W24"/>
+    <mergeCell ref="X24:Z24"/>
+    <mergeCell ref="AA24:AD24"/>
+    <mergeCell ref="U25:W25"/>
+    <mergeCell ref="X25:Z25"/>
+    <mergeCell ref="AA25:AD25"/>
+    <mergeCell ref="U27:W27"/>
+    <mergeCell ref="X27:Z27"/>
+    <mergeCell ref="AA27:AD27"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="AO11:AQ11"/>
+    <mergeCell ref="AR11:AT11"/>
+    <mergeCell ref="AU11:AX11"/>
+    <mergeCell ref="AO12:AQ12"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="AA11:AD11"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X12:Z12"/>
+    <mergeCell ref="AA12:AD12"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="X13:Z13"/>
+    <mergeCell ref="AA13:AD13"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="AM3:AR3"/>
+    <mergeCell ref="AS3:AX3"/>
+    <mergeCell ref="K5:U5"/>
+    <mergeCell ref="AM4:AX4"/>
+    <mergeCell ref="AM5:AX5"/>
+    <mergeCell ref="A1:AX1"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="J7:R7"/>
+    <mergeCell ref="AI5:AL5"/>
+    <mergeCell ref="AE5:AH5"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="U9:AD9"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="X10:Z10"/>
+    <mergeCell ref="AA10:AD10"/>
+    <mergeCell ref="AO9:AX9"/>
+    <mergeCell ref="AO10:AQ10"/>
+    <mergeCell ref="AR10:AT10"/>
+    <mergeCell ref="AU10:AX10"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="U26:W26"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="X26:Z26"/>
+    <mergeCell ref="AA26:AD26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="U30:W30"/>
+    <mergeCell ref="X30:Z30"/>
+    <mergeCell ref="AA30:AD30"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="J32:R32"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="U28:W28"/>
+    <mergeCell ref="X28:Z28"/>
+    <mergeCell ref="AA28:AD28"/>
+    <mergeCell ref="U29:W29"/>
+    <mergeCell ref="X29:Z29"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="X14:Z14"/>
+    <mergeCell ref="AA14:AD14"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="X15:Z15"/>
+    <mergeCell ref="AA15:AD15"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="AA16:AD16"/>
+    <mergeCell ref="U17:W17"/>
+    <mergeCell ref="X17:Z17"/>
+    <mergeCell ref="AA17:AD17"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="X21:Z21"/>
+    <mergeCell ref="AA21:AD21"/>
+    <mergeCell ref="U22:W22"/>
+    <mergeCell ref="X22:Z22"/>
+    <mergeCell ref="AA22:AD22"/>
+    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="X18:Z18"/>
+    <mergeCell ref="AA18:AD18"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="AA19:AD19"/>
+    <mergeCell ref="X20:Z20"/>
+    <mergeCell ref="AA20:AD20"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="69" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="70" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/WEB-INF/templateFile/KinYukyuKyukaDaicho.xlsx
+++ b/WEB-INF/templateFile/KinYukyuKyukaDaicho.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\Kintai\workspace\Kintai\WEB-INF\templateFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BEB0C7-9630-4B34-8627-78EFDF61BA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00CD9BB-1F35-4A5C-B3C6-68857544E99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,39 +132,44 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="BIZ UDゴシック"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="BIZ UDゴシック"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="22"/>
-      <color theme="1"/>
-      <name val="BIZ UDゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="BIZ UDゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="BIZ UDゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -251,48 +256,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -302,59 +307,59 @@
     <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -640,169 +645,169 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AX65"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="50" width="2.59765625" style="1" customWidth="1"/>
     <col min="51" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="27"/>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
-      <c r="AH1" s="27"/>
-      <c r="AI1" s="27"/>
-      <c r="AJ1" s="27"/>
-      <c r="AK1" s="27"/>
-      <c r="AL1" s="27"/>
-      <c r="AM1" s="27"/>
-      <c r="AN1" s="27"/>
-      <c r="AO1" s="27"/>
-      <c r="AP1" s="27"/>
-      <c r="AQ1" s="27"/>
-      <c r="AR1" s="27"/>
-      <c r="AS1" s="27"/>
-      <c r="AT1" s="27"/>
-      <c r="AU1" s="27"/>
-      <c r="AV1" s="27"/>
-      <c r="AW1" s="27"/>
-      <c r="AX1" s="27"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="22"/>
+      <c r="AK1" s="22"/>
+      <c r="AL1" s="22"/>
+      <c r="AM1" s="22"/>
+      <c r="AN1" s="22"/>
+      <c r="AO1" s="22"/>
+      <c r="AP1" s="22"/>
+      <c r="AQ1" s="22"/>
+      <c r="AR1" s="22"/>
+      <c r="AS1" s="22"/>
+      <c r="AT1" s="22"/>
+      <c r="AU1" s="22"/>
+      <c r="AV1" s="22"/>
+      <c r="AW1" s="22"/>
+      <c r="AX1" s="22"/>
     </row>
     <row r="2" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="3" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="AM3" s="23"/>
-      <c r="AN3" s="23"/>
-      <c r="AO3" s="23"/>
-      <c r="AP3" s="23"/>
-      <c r="AQ3" s="23"/>
-      <c r="AR3" s="23"/>
-      <c r="AS3" s="24"/>
-      <c r="AT3" s="24"/>
-      <c r="AU3" s="24"/>
-      <c r="AV3" s="24"/>
-      <c r="AW3" s="24"/>
-      <c r="AX3" s="24"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="32"/>
+      <c r="AO3" s="32"/>
+      <c r="AP3" s="32"/>
+      <c r="AQ3" s="32"/>
+      <c r="AR3" s="32"/>
+      <c r="AS3" s="33"/>
+      <c r="AT3" s="33"/>
+      <c r="AU3" s="33"/>
+      <c r="AV3" s="33"/>
+      <c r="AW3" s="33"/>
+      <c r="AX3" s="33"/>
     </row>
     <row r="4" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="AM4" s="26"/>
-      <c r="AN4" s="26"/>
-      <c r="AO4" s="26"/>
-      <c r="AP4" s="26"/>
-      <c r="AQ4" s="26"/>
-      <c r="AR4" s="26"/>
-      <c r="AS4" s="26"/>
-      <c r="AT4" s="26"/>
-      <c r="AU4" s="26"/>
-      <c r="AV4" s="26"/>
-      <c r="AW4" s="26"/>
-      <c r="AX4" s="26"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="35"/>
+      <c r="AO4" s="35"/>
+      <c r="AP4" s="35"/>
+      <c r="AQ4" s="35"/>
+      <c r="AR4" s="35"/>
+      <c r="AS4" s="35"/>
+      <c r="AT4" s="35"/>
+      <c r="AU4" s="35"/>
+      <c r="AV4" s="35"/>
+      <c r="AW4" s="35"/>
+      <c r="AX4" s="35"/>
     </row>
     <row r="5" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="34"/>
-      <c r="U5" s="34"/>
-      <c r="AE5" s="31" t="s">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="AE5" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="AF5" s="32"/>
-      <c r="AG5" s="32"/>
-      <c r="AH5" s="33"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="30"/>
-      <c r="AM5" s="34"/>
-      <c r="AN5" s="34"/>
-      <c r="AO5" s="34"/>
-      <c r="AP5" s="34"/>
-      <c r="AQ5" s="34"/>
-      <c r="AR5" s="34"/>
-      <c r="AS5" s="34"/>
-      <c r="AT5" s="34"/>
-      <c r="AU5" s="34"/>
-      <c r="AV5" s="34"/>
-      <c r="AW5" s="34"/>
-      <c r="AX5" s="34"/>
+      <c r="AF5" s="27"/>
+      <c r="AG5" s="27"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="23"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
+      <c r="AL5" s="25"/>
+      <c r="AM5" s="30"/>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="30"/>
+      <c r="AP5" s="30"/>
+      <c r="AQ5" s="30"/>
+      <c r="AR5" s="30"/>
+      <c r="AS5" s="30"/>
+      <c r="AT5" s="30"/>
+      <c r="AU5" s="30"/>
+      <c r="AV5" s="30"/>
+      <c r="AW5" s="30"/>
+      <c r="AX5" s="30"/>
     </row>
     <row r="6" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="7" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -826,56 +831,56 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="21"/>
       <c r="R7" s="21"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="11"/>
-      <c r="AB7" s="10"/>
-      <c r="AC7" s="10"/>
-      <c r="AD7" s="10"/>
-      <c r="AE7" s="10"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="4"/>
+      <c r="AC7" s="4"/>
+      <c r="AD7" s="4"/>
+      <c r="AE7" s="4"/>
     </row>
     <row r="8" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="9" spans="1:50" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
-      <c r="U9" s="22" t="s">
+      <c r="U9" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="22"/>
-      <c r="AD9" s="22"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="31"/>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="31"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
       <c r="AG9" s="7"/>
@@ -886,62 +891,62 @@
       <c r="AL9" s="7"/>
       <c r="AM9" s="7"/>
       <c r="AN9" s="7"/>
-      <c r="AO9" s="22" t="s">
+      <c r="AO9" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="AP9" s="22"/>
-      <c r="AQ9" s="22"/>
-      <c r="AR9" s="22"/>
-      <c r="AS9" s="22"/>
-      <c r="AT9" s="22"/>
-      <c r="AU9" s="22"/>
-      <c r="AV9" s="22"/>
-      <c r="AW9" s="22"/>
-      <c r="AX9" s="22"/>
+      <c r="AP9" s="31"/>
+      <c r="AQ9" s="31"/>
+      <c r="AR9" s="31"/>
+      <c r="AS9" s="31"/>
+      <c r="AT9" s="31"/>
+      <c r="AU9" s="31"/>
+      <c r="AV9" s="31"/>
+      <c r="AW9" s="31"/>
+      <c r="AX9" s="31"/>
     </row>
     <row r="10" spans="1:50" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22" t="s">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
-      <c r="U10" s="22" t="s">
+      <c r="U10" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22" t="s">
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22" t="s">
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="22"/>
-      <c r="AD10" s="22"/>
+      <c r="AB10" s="31"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="31"/>
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
       <c r="AG10" s="7"/>
@@ -952,22 +957,22 @@
       <c r="AL10" s="7"/>
       <c r="AM10" s="7"/>
       <c r="AN10" s="7"/>
-      <c r="AO10" s="22" t="s">
+      <c r="AO10" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="AP10" s="22"/>
-      <c r="AQ10" s="22"/>
-      <c r="AR10" s="22" t="s">
+      <c r="AP10" s="31"/>
+      <c r="AQ10" s="31"/>
+      <c r="AR10" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="AS10" s="22"/>
-      <c r="AT10" s="22"/>
-      <c r="AU10" s="22" t="s">
+      <c r="AS10" s="31"/>
+      <c r="AT10" s="31"/>
+      <c r="AU10" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="AV10" s="22"/>
-      <c r="AW10" s="22"/>
-      <c r="AX10" s="22"/>
+      <c r="AV10" s="31"/>
+      <c r="AW10" s="31"/>
+      <c r="AX10" s="31"/>
     </row>
     <row r="11" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="15"/>
@@ -980,16 +985,16 @@
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="14"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="9"/>
       <c r="U11" s="15"/>
       <c r="V11" s="15"/>
       <c r="W11" s="15"/>
@@ -1032,16 +1037,16 @@
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="14"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="9"/>
       <c r="U12" s="15"/>
       <c r="V12" s="15"/>
       <c r="W12" s="15"/>
@@ -1084,16 +1089,16 @@
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="14"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="9"/>
       <c r="U13" s="15"/>
       <c r="V13" s="15"/>
       <c r="W13" s="15"/>
@@ -1106,12 +1111,12 @@
       <c r="AD13" s="17"/>
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
-      <c r="AG13" s="8"/>
+      <c r="AG13" s="10"/>
       <c r="AH13" s="7"/>
       <c r="AI13" s="7"/>
-      <c r="AJ13" s="9"/>
-      <c r="AK13" s="9"/>
-      <c r="AL13" s="9"/>
+      <c r="AJ13" s="8"/>
+      <c r="AK13" s="8"/>
+      <c r="AL13" s="8"/>
       <c r="AM13" s="7"/>
       <c r="AN13" s="7"/>
       <c r="AO13" s="15"/>
@@ -1136,16 +1141,16 @@
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="14"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="9"/>
       <c r="U14" s="15"/>
       <c r="V14" s="15"/>
       <c r="W14" s="15"/>
@@ -1188,16 +1193,16 @@
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="14"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="9"/>
       <c r="U15" s="15"/>
       <c r="V15" s="15"/>
       <c r="W15" s="15"/>
@@ -1210,12 +1215,12 @@
       <c r="AD15" s="17"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
-      <c r="AG15" s="8"/>
+      <c r="AG15" s="10"/>
       <c r="AH15" s="7"/>
       <c r="AI15" s="7"/>
-      <c r="AJ15" s="9"/>
-      <c r="AK15" s="9"/>
-      <c r="AL15" s="9"/>
+      <c r="AJ15" s="8"/>
+      <c r="AK15" s="8"/>
+      <c r="AL15" s="8"/>
       <c r="AM15" s="7"/>
       <c r="AN15" s="7"/>
       <c r="AO15" s="15"/>
@@ -1240,16 +1245,16 @@
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="14"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="9"/>
       <c r="U16" s="15"/>
       <c r="V16" s="15"/>
       <c r="W16" s="15"/>
@@ -1292,16 +1297,16 @@
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="14"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="9"/>
       <c r="U17" s="15"/>
       <c r="V17" s="15"/>
       <c r="W17" s="15"/>
@@ -1314,12 +1319,12 @@
       <c r="AD17" s="17"/>
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
-      <c r="AG17" s="8"/>
+      <c r="AG17" s="10"/>
       <c r="AH17" s="7"/>
       <c r="AI17" s="7"/>
-      <c r="AJ17" s="9"/>
-      <c r="AK17" s="9"/>
-      <c r="AL17" s="9"/>
+      <c r="AJ17" s="8"/>
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="8"/>
       <c r="AM17" s="7"/>
       <c r="AN17" s="7"/>
       <c r="AO17" s="15"/>
@@ -1344,16 +1349,16 @@
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="14"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="9"/>
       <c r="U18" s="15"/>
       <c r="V18" s="15"/>
       <c r="W18" s="15"/>
@@ -1396,16 +1401,16 @@
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="14"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="9"/>
       <c r="U19" s="15"/>
       <c r="V19" s="15"/>
       <c r="W19" s="15"/>
@@ -1448,16 +1453,16 @@
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="14"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="9"/>
       <c r="U20" s="15"/>
       <c r="V20" s="15"/>
       <c r="W20" s="15"/>
@@ -1500,16 +1505,16 @@
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="14"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="9"/>
       <c r="U21" s="15"/>
       <c r="V21" s="15"/>
       <c r="W21" s="15"/>
@@ -1552,16 +1557,16 @@
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="14"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="9"/>
       <c r="U22" s="15"/>
       <c r="V22" s="15"/>
       <c r="W22" s="15"/>
@@ -1604,16 +1609,16 @@
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="14"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="9"/>
       <c r="U23" s="15"/>
       <c r="V23" s="15"/>
       <c r="W23" s="15"/>
@@ -1656,16 +1661,16 @@
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="14"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="9"/>
       <c r="U24" s="15"/>
       <c r="V24" s="15"/>
       <c r="W24" s="15"/>
@@ -1708,16 +1713,16 @@
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="14"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="9"/>
       <c r="U25" s="15"/>
       <c r="V25" s="15"/>
       <c r="W25" s="15"/>
@@ -1760,16 +1765,16 @@
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="14"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="9"/>
       <c r="U26" s="15"/>
       <c r="V26" s="15"/>
       <c r="W26" s="15"/>
@@ -1812,16 +1817,16 @@
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="14"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="9"/>
       <c r="U27" s="15"/>
       <c r="V27" s="15"/>
       <c r="W27" s="15"/>
@@ -1864,16 +1869,16 @@
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
       <c r="J28" s="17"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="14"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="9"/>
       <c r="U28" s="15"/>
       <c r="V28" s="15"/>
       <c r="W28" s="15"/>
@@ -1916,16 +1921,16 @@
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
       <c r="J29" s="17"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="14"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="9"/>
       <c r="U29" s="15"/>
       <c r="V29" s="15"/>
       <c r="W29" s="15"/>
@@ -1968,16 +1973,16 @@
       <c r="H30" s="17"/>
       <c r="I30" s="17"/>
       <c r="J30" s="17"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="14"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="9"/>
       <c r="U30" s="15"/>
       <c r="V30" s="15"/>
       <c r="W30" s="15"/>
@@ -2010,34 +2015,34 @@
       <c r="AX30" s="17"/>
     </row>
     <row r="31" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="14"/>
-      <c r="AB31" s="14"/>
+      <c r="Z31" s="8"/>
+      <c r="AA31" s="9"/>
+      <c r="AB31" s="9"/>
       <c r="AC31" s="7"/>
       <c r="AD31" s="7"/>
       <c r="AE31" s="7"/>
@@ -2082,16 +2087,16 @@
       <c r="P32" s="21"/>
       <c r="Q32" s="21"/>
       <c r="R32" s="21"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
+      <c r="S32" s="8"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
       <c r="V32" s="7"/>
       <c r="W32" s="7"/>
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
-      <c r="Z32" s="9"/>
-      <c r="AA32" s="14"/>
-      <c r="AB32" s="14"/>
+      <c r="Z32" s="8"/>
+      <c r="AA32" s="9"/>
+      <c r="AB32" s="9"/>
       <c r="AC32" s="7"/>
       <c r="AD32" s="7"/>
       <c r="AE32" s="7"/>
@@ -2116,34 +2121,34 @@
       <c r="AX32" s="7"/>
     </row>
     <row r="33" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
       <c r="O33" s="7"/>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
-      <c r="Z33" s="9"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
+      <c r="Z33" s="8"/>
+      <c r="AA33" s="9"/>
+      <c r="AB33" s="9"/>
       <c r="AC33" s="7"/>
       <c r="AD33" s="7"/>
       <c r="AE33" s="7"/>
@@ -2168,34 +2173,34 @@
       <c r="AX33" s="7"/>
     </row>
     <row r="34" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
       <c r="O34" s="7"/>
       <c r="P34" s="7"/>
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14"/>
+      <c r="S34" s="8"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
       <c r="X34" s="7"/>
       <c r="Y34" s="7"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="14"/>
-      <c r="AB34" s="14"/>
+      <c r="Z34" s="8"/>
+      <c r="AA34" s="9"/>
+      <c r="AB34" s="9"/>
       <c r="AC34" s="7"/>
       <c r="AD34" s="7"/>
       <c r="AE34" s="7"/>
@@ -2220,34 +2225,34 @@
       <c r="AX34" s="7"/>
     </row>
     <row r="35" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="13"/>
-      <c r="B35" s="13"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
       <c r="O35" s="7"/>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="14"/>
-      <c r="U35" s="14"/>
+      <c r="S35" s="8"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
       <c r="V35" s="7"/>
       <c r="W35" s="7"/>
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
-      <c r="Z35" s="9"/>
-      <c r="AA35" s="14"/>
-      <c r="AB35" s="14"/>
+      <c r="Z35" s="8"/>
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="9"/>
       <c r="AC35" s="7"/>
       <c r="AD35" s="7"/>
       <c r="AE35" s="7"/>
@@ -2272,34 +2277,34 @@
       <c r="AX35" s="7"/>
     </row>
     <row r="36" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
-      <c r="S36" s="9"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14"/>
+      <c r="S36" s="8"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
       <c r="V36" s="7"/>
       <c r="W36" s="7"/>
       <c r="X36" s="7"/>
       <c r="Y36" s="7"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="14"/>
-      <c r="AB36" s="14"/>
+      <c r="Z36" s="8"/>
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="9"/>
       <c r="AC36" s="7"/>
       <c r="AD36" s="7"/>
       <c r="AE36" s="7"/>
@@ -2324,34 +2329,34 @@
       <c r="AX36" s="7"/>
     </row>
     <row r="37" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
       <c r="O37" s="7"/>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
+      <c r="S37" s="8"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
       <c r="V37" s="7"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
-      <c r="Z37" s="9"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
+      <c r="Z37" s="8"/>
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="9"/>
       <c r="AC37" s="7"/>
       <c r="AD37" s="7"/>
       <c r="AE37" s="7"/>
@@ -2376,34 +2381,34 @@
       <c r="AX37" s="7"/>
     </row>
     <row r="38" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="13"/>
-      <c r="B38" s="13"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
       <c r="O38" s="7"/>
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
       <c r="R38" s="7"/>
-      <c r="S38" s="9"/>
-      <c r="T38" s="14"/>
-      <c r="U38" s="14"/>
+      <c r="S38" s="8"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
       <c r="V38" s="7"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
-      <c r="Z38" s="9"/>
-      <c r="AA38" s="14"/>
-      <c r="AB38" s="14"/>
+      <c r="Z38" s="8"/>
+      <c r="AA38" s="9"/>
+      <c r="AB38" s="9"/>
       <c r="AC38" s="7"/>
       <c r="AD38" s="7"/>
       <c r="AE38" s="7"/>
@@ -2428,34 +2433,34 @@
       <c r="AX38" s="7"/>
     </row>
     <row r="39" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
       <c r="O39" s="7"/>
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="14"/>
-      <c r="U39" s="14"/>
+      <c r="S39" s="8"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="14"/>
-      <c r="AB39" s="14"/>
+      <c r="Z39" s="8"/>
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="9"/>
       <c r="AC39" s="7"/>
       <c r="AD39" s="7"/>
       <c r="AE39" s="7"/>
@@ -2480,34 +2485,34 @@
       <c r="AX39" s="7"/>
     </row>
     <row r="40" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
-      <c r="S40" s="9"/>
-      <c r="T40" s="14"/>
-      <c r="U40" s="14"/>
+      <c r="S40" s="8"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
       <c r="V40" s="7"/>
       <c r="W40" s="7"/>
       <c r="X40" s="7"/>
       <c r="Y40" s="7"/>
-      <c r="Z40" s="9"/>
-      <c r="AA40" s="14"/>
-      <c r="AB40" s="14"/>
+      <c r="Z40" s="8"/>
+      <c r="AA40" s="9"/>
+      <c r="AB40" s="9"/>
       <c r="AC40" s="7"/>
       <c r="AD40" s="7"/>
       <c r="AE40" s="7"/>
@@ -2532,34 +2537,34 @@
       <c r="AX40" s="7"/>
     </row>
     <row r="41" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
       <c r="O41" s="7"/>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="14"/>
-      <c r="U41" s="14"/>
+      <c r="S41" s="8"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
-      <c r="Z41" s="9"/>
-      <c r="AA41" s="14"/>
-      <c r="AB41" s="14"/>
+      <c r="Z41" s="8"/>
+      <c r="AA41" s="9"/>
+      <c r="AB41" s="9"/>
       <c r="AC41" s="7"/>
       <c r="AD41" s="7"/>
       <c r="AE41" s="7"/>
@@ -2584,46 +2589,46 @@
       <c r="AX41" s="7"/>
     </row>
     <row r="42" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
-      <c r="AB42" s="4"/>
-      <c r="AC42" s="4"/>
-      <c r="AD42" s="4"/>
-      <c r="AE42" s="4"/>
-      <c r="AF42" s="4"/>
-      <c r="AG42" s="4"/>
-      <c r="AH42" s="4"/>
-      <c r="AI42" s="4"/>
-      <c r="AJ42" s="4"/>
-      <c r="AK42" s="4"/>
-      <c r="AL42" s="4"/>
-      <c r="AM42" s="4"/>
-      <c r="AN42" s="4"/>
+      <c r="A42" s="12"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
+      <c r="P42" s="14"/>
+      <c r="Q42" s="14"/>
+      <c r="R42" s="14"/>
+      <c r="S42" s="14"/>
+      <c r="T42" s="14"/>
+      <c r="U42" s="14"/>
+      <c r="V42" s="14"/>
+      <c r="W42" s="14"/>
+      <c r="X42" s="14"/>
+      <c r="Y42" s="14"/>
+      <c r="Z42" s="14"/>
+      <c r="AA42" s="14"/>
+      <c r="AB42" s="14"/>
+      <c r="AC42" s="14"/>
+      <c r="AD42" s="14"/>
+      <c r="AE42" s="14"/>
+      <c r="AF42" s="14"/>
+      <c r="AG42" s="14"/>
+      <c r="AH42" s="14"/>
+      <c r="AI42" s="14"/>
+      <c r="AJ42" s="14"/>
+      <c r="AK42" s="14"/>
+      <c r="AL42" s="14"/>
+      <c r="AM42" s="14"/>
+      <c r="AN42" s="14"/>
     </row>
     <row r="43" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="44" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -2631,23 +2636,23 @@
     <row r="46" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="47" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="48" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="49" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="50" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="51" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="52" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="53" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="54" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="55" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="56" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="57" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="58" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="59" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="60" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="61" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="62" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="63" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="64" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="65" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="206">
     <mergeCell ref="AO29:AQ29"/>
@@ -2683,12 +2688,15 @@
     <mergeCell ref="AO22:AQ22"/>
     <mergeCell ref="AR22:AT22"/>
     <mergeCell ref="AU22:AX22"/>
-    <mergeCell ref="AA29:AD29"/>
-    <mergeCell ref="AR12:AT12"/>
-    <mergeCell ref="AU12:AX12"/>
-    <mergeCell ref="AO13:AQ13"/>
-    <mergeCell ref="AR13:AT13"/>
-    <mergeCell ref="AU13:AX13"/>
+    <mergeCell ref="AO17:AQ17"/>
+    <mergeCell ref="AR17:AT17"/>
+    <mergeCell ref="AU17:AX17"/>
+    <mergeCell ref="AO18:AQ18"/>
+    <mergeCell ref="AR18:AT18"/>
+    <mergeCell ref="AU18:AX18"/>
+    <mergeCell ref="AO19:AQ19"/>
+    <mergeCell ref="AR19:AT19"/>
+    <mergeCell ref="AU19:AX19"/>
     <mergeCell ref="AO14:AQ14"/>
     <mergeCell ref="AR14:AT14"/>
     <mergeCell ref="AU14:AX14"/>
@@ -2698,26 +2706,6 @@
     <mergeCell ref="AO16:AQ16"/>
     <mergeCell ref="AR16:AT16"/>
     <mergeCell ref="AU16:AX16"/>
-    <mergeCell ref="AO17:AQ17"/>
-    <mergeCell ref="AR17:AT17"/>
-    <mergeCell ref="AU17:AX17"/>
-    <mergeCell ref="AO18:AQ18"/>
-    <mergeCell ref="AR18:AT18"/>
-    <mergeCell ref="AU18:AX18"/>
-    <mergeCell ref="AO19:AQ19"/>
-    <mergeCell ref="AR19:AT19"/>
-    <mergeCell ref="AU19:AX19"/>
-    <mergeCell ref="X23:Z23"/>
-    <mergeCell ref="AA23:AD23"/>
-    <mergeCell ref="U24:W24"/>
-    <mergeCell ref="X24:Z24"/>
-    <mergeCell ref="AA24:AD24"/>
-    <mergeCell ref="U25:W25"/>
-    <mergeCell ref="X25:Z25"/>
-    <mergeCell ref="AA25:AD25"/>
-    <mergeCell ref="U27:W27"/>
-    <mergeCell ref="X27:Z27"/>
-    <mergeCell ref="AA27:AD27"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="G19:J19"/>
@@ -2728,6 +2716,14 @@
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:F23"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="G16:J16"/>
@@ -2737,10 +2733,6 @@
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="G18:J18"/>
-    <mergeCell ref="AO11:AQ11"/>
-    <mergeCell ref="AR11:AT11"/>
-    <mergeCell ref="AU11:AX11"/>
-    <mergeCell ref="AO12:AQ12"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="G14:J14"/>
@@ -2770,6 +2762,15 @@
     <mergeCell ref="K5:U5"/>
     <mergeCell ref="AM4:AX4"/>
     <mergeCell ref="AM5:AX5"/>
+    <mergeCell ref="AO11:AQ11"/>
+    <mergeCell ref="AR11:AT11"/>
+    <mergeCell ref="AU11:AX11"/>
+    <mergeCell ref="AO12:AQ12"/>
+    <mergeCell ref="AR12:AT12"/>
+    <mergeCell ref="AU12:AX12"/>
+    <mergeCell ref="AO13:AQ13"/>
+    <mergeCell ref="AR13:AT13"/>
+    <mergeCell ref="AU13:AX13"/>
     <mergeCell ref="A1:AX1"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="J7:R7"/>
@@ -2789,15 +2790,6 @@
     <mergeCell ref="AO10:AQ10"/>
     <mergeCell ref="AR10:AT10"/>
     <mergeCell ref="AU10:AX10"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="U26:W26"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="G26:J26"/>
@@ -2807,6 +2799,18 @@
     <mergeCell ref="AA26:AD26"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="D27:F27"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="AA23:AD23"/>
+    <mergeCell ref="U24:W24"/>
+    <mergeCell ref="X24:Z24"/>
+    <mergeCell ref="AA24:AD24"/>
+    <mergeCell ref="U25:W25"/>
+    <mergeCell ref="X25:Z25"/>
+    <mergeCell ref="AA25:AD25"/>
+    <mergeCell ref="U27:W27"/>
+    <mergeCell ref="X27:Z27"/>
+    <mergeCell ref="AA27:AD27"/>
+    <mergeCell ref="U26:W26"/>
     <mergeCell ref="U30:W30"/>
     <mergeCell ref="X30:Z30"/>
     <mergeCell ref="AA30:AD30"/>
@@ -2827,6 +2831,7 @@
     <mergeCell ref="AA28:AD28"/>
     <mergeCell ref="U29:W29"/>
     <mergeCell ref="X29:Z29"/>
+    <mergeCell ref="AA29:AD29"/>
     <mergeCell ref="U14:W14"/>
     <mergeCell ref="X14:Z14"/>
     <mergeCell ref="AA14:AD14"/>
